--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="88">
   <si>
     <t>인수기관</t>
   </si>
@@ -55,9 +55,6 @@
     <t>BNK</t>
   </si>
   <si>
-    <t>DB</t>
-  </si>
-  <si>
     <t>IBK</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>2024-06-14</t>
   </si>
   <si>
-    <t>2024-06-05</t>
-  </si>
-  <si>
     <t>2024-06-10</t>
   </si>
   <si>
@@ -112,12 +106,12 @@
     <t>2024-07-02</t>
   </si>
   <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -142,18 +136,15 @@
     <t>2024-07-22</t>
   </si>
   <si>
+    <t>2024-06-17</t>
+  </si>
+  <si>
     <t>2024-06-18</t>
   </si>
   <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
     <t>에스오에스랩</t>
   </si>
   <si>
-    <t>디비금융스팩12호</t>
-  </si>
-  <si>
     <t>한중엔시에스</t>
   </si>
   <si>
@@ -163,21 +154,18 @@
     <t>이베스트스팩6호</t>
   </si>
   <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
     <t>에이치브이엠</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
-    <t>라메디텍</t>
-  </si>
-  <si>
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
@@ -205,18 +193,18 @@
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
+    <t>한국제15호스팩</t>
+  </si>
+  <si>
+    <t>한국제14호스팩</t>
+  </si>
+  <si>
+    <t>씨어스테크놀로지</t>
+  </si>
+  <si>
     <t>하이젠알앤엠</t>
   </si>
   <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
-    <t>한국제14호스팩</t>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-  </si>
-  <si>
     <t>에이치엠씨제7호스팩</t>
   </si>
   <si>
@@ -268,13 +256,13 @@
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>2024-07-26</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
     <t>2024-06-28</t>
-  </si>
-  <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
   </si>
   <si>
     <t>2024-07-29</t>
@@ -647,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -693,22 +681,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>1150</v>
@@ -731,10 +719,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -743,19 +731,19 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H3">
-        <v>10000</v>
+        <v>48000</v>
       </c>
       <c r="I3">
-        <v>5000000</v>
+        <v>1600000</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -769,10 +757,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -781,19 +769,19 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="H4">
-        <v>48000</v>
+        <v>12000</v>
       </c>
       <c r="I4">
-        <v>1600000</v>
+        <v>6000000</v>
       </c>
       <c r="J4">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -807,28 +795,28 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H5">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I5">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="J5">
         <v>2000</v>
@@ -845,28 +833,28 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="J6">
         <v>2000</v>
@@ -880,72 +868,72 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H7">
-        <v>43200</v>
+        <v>130500</v>
       </c>
       <c r="I7">
-        <v>2400000</v>
+        <v>7250000</v>
       </c>
       <c r="J7">
-        <v>18000</v>
+        <v>60000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H8">
-        <v>12000</v>
+        <v>43200</v>
       </c>
       <c r="I8">
-        <v>6000000</v>
+        <v>2400000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -959,37 +947,37 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>130500</v>
+        <v>8000</v>
       </c>
       <c r="I9">
-        <v>7250000</v>
+        <v>4000000</v>
       </c>
       <c r="J9">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -997,10 +985,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -1009,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H10">
-        <v>8000</v>
+        <v>16180</v>
       </c>
       <c r="I10">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1035,37 +1023,37 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="H11">
-        <v>20768</v>
+        <v>255360</v>
       </c>
       <c r="I11">
-        <v>1298000</v>
+        <v>7600000</v>
       </c>
       <c r="J11">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1073,10 +1061,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -1085,19 +1073,19 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12">
-        <v>16180</v>
+        <v>9500</v>
       </c>
       <c r="I12">
-        <v>1618000</v>
+        <v>4750000</v>
       </c>
       <c r="J12">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1108,78 +1096,78 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>255360</v>
+        <v>12900</v>
       </c>
       <c r="I13">
-        <v>7600000</v>
+        <v>6450000</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
       <c r="H14">
-        <v>9500</v>
+        <v>54133.66</v>
       </c>
       <c r="I14">
-        <v>4750000</v>
+        <v>1330000</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>43300</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1190,7 +1178,7 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -1199,19 +1187,19 @@
         <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H15">
-        <v>12900</v>
+        <v>22340</v>
       </c>
       <c r="I15">
-        <v>6450000</v>
+        <v>2234000</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1225,69 +1213,69 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
         <v>74</v>
       </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="H16">
-        <v>54133.66</v>
+        <v>10640</v>
       </c>
       <c r="I16">
-        <v>1330000</v>
+        <v>7600000</v>
       </c>
       <c r="J16">
-        <v>43300</v>
+        <v>35000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>94</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>22340</v>
+        <v>28960</v>
       </c>
       <c r="I17">
-        <v>2234000</v>
+        <v>1810000</v>
       </c>
       <c r="J17">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1301,37 +1289,37 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>28960</v>
+        <v>3455.34</v>
       </c>
       <c r="I18">
-        <v>1810000</v>
+        <v>1330000</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>43300</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1339,75 +1327,75 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H19">
-        <v>10640</v>
+        <v>35000.001</v>
       </c>
       <c r="I19">
-        <v>7600000</v>
+        <v>23333334</v>
       </c>
       <c r="J19">
-        <v>35000</v>
+        <v>3000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="H20">
-        <v>3455.34</v>
+        <v>17400</v>
       </c>
       <c r="I20">
-        <v>1330000</v>
+        <v>7250000</v>
       </c>
       <c r="J20">
-        <v>43300</v>
+        <v>60000</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1415,25 +1403,25 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H21">
-        <v>17400</v>
+        <v>143550</v>
       </c>
       <c r="I21">
         <v>7250000</v>
@@ -1445,83 +1433,83 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
         <v>37</v>
       </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>42</v>
-      </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H22">
-        <v>35000.001</v>
+        <v>29700</v>
       </c>
       <c r="I22">
-        <v>23333334</v>
+        <v>1350000</v>
       </c>
       <c r="J22">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23">
-        <v>143550</v>
+        <v>12500</v>
       </c>
       <c r="I23">
-        <v>7250000</v>
+        <v>6250000</v>
       </c>
       <c r="J23">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1529,69 +1517,69 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H24">
-        <v>29700</v>
+        <v>21850</v>
       </c>
       <c r="I24">
-        <v>1350000</v>
+        <v>2000000</v>
       </c>
       <c r="J24">
-        <v>22000</v>
+        <v>11500</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="H25">
-        <v>23800</v>
+        <v>8000</v>
       </c>
       <c r="I25">
-        <v>3400000</v>
+        <v>4000000</v>
       </c>
       <c r="J25">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1602,110 +1590,110 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H26">
-        <v>12500</v>
+        <v>143550</v>
       </c>
       <c r="I26">
-        <v>6250000</v>
+        <v>7250000</v>
       </c>
       <c r="J26">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="H27">
-        <v>21850</v>
+        <v>22100</v>
       </c>
       <c r="I27">
-        <v>2000000</v>
+        <v>1300000</v>
       </c>
       <c r="J27">
-        <v>11500</v>
+        <v>17000</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="H28">
-        <v>8000</v>
+        <v>23800</v>
       </c>
       <c r="I28">
-        <v>4000000</v>
+        <v>3400000</v>
       </c>
       <c r="J28">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -1716,40 +1704,40 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
         <v>66</v>
       </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H29">
-        <v>22100</v>
+        <v>35000.001</v>
       </c>
       <c r="I29">
-        <v>1300000</v>
+        <v>23333334</v>
       </c>
       <c r="J29">
-        <v>17000</v>
+        <v>3000</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1757,112 +1745,36 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="H30">
-        <v>143550</v>
+        <v>14000</v>
       </c>
       <c r="I30">
-        <v>7250000</v>
+        <v>7000000</v>
       </c>
       <c r="J30">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31">
-        <v>35000.001</v>
-      </c>
-      <c r="I31">
-        <v>23333334</v>
-      </c>
-      <c r="J31">
-        <v>3000</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" t="s">
-        <v>40</v>
-      </c>
-      <c r="H32">
-        <v>14000</v>
-      </c>
-      <c r="I32">
-        <v>7000000</v>
-      </c>
-      <c r="J32">
-        <v>2000</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
   <si>
     <t>인수기관</t>
   </si>
@@ -55,9 +55,6 @@
     <t>BNK</t>
   </si>
   <si>
-    <t>IBK</t>
-  </si>
-  <si>
     <t>KB</t>
   </si>
   <si>
@@ -97,114 +94,105 @@
     <t>2024-06-14</t>
   </si>
   <si>
-    <t>2024-06-10</t>
-  </si>
-  <si>
     <t>2024-06-11</t>
   </si>
   <si>
     <t>2024-07-02</t>
   </si>
   <si>
+    <t>2024-06-19</t>
+  </si>
+  <si>
     <t>2024-07-16</t>
   </si>
   <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
     <t>2024-07-03</t>
   </si>
   <si>
+    <t>2024-06-13</t>
+  </si>
+  <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
     <t>2024-07-18</t>
   </si>
   <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
-    <t>2024-06-20</t>
+    <t>2024-06-24</t>
   </si>
   <si>
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>2024-07-22</t>
   </si>
   <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
     <t>2024-06-17</t>
   </si>
   <si>
-    <t>2024-06-18</t>
-  </si>
-  <si>
     <t>에스오에스랩</t>
   </si>
   <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
     <t>KB제29호스팩</t>
   </si>
   <si>
     <t>이베스트스팩6호</t>
   </si>
   <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
     <t>시프트업</t>
   </si>
   <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
+    <t>미래에셋비전스팩6호</t>
+  </si>
+  <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>산일전기</t>
   </si>
   <si>
-    <t>미래에셋비전스팩5호</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
+    <t>하스</t>
   </si>
   <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>하스</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
+    <t>하이젠알앤엠</t>
+  </si>
+  <si>
     <t>한국제15호스팩</t>
   </si>
   <si>
-    <t>한국제14호스팩</t>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-  </si>
-  <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
     <t>에이치엠씨제7호스팩</t>
   </si>
   <si>
@@ -223,12 +211,12 @@
     <t>한국, 제이피모간회사 서울지점, NH, 신한</t>
   </si>
   <si>
+    <t>미래, 신한</t>
+  </si>
+  <si>
     <t>미래, 삼성</t>
   </si>
   <si>
-    <t>미래, 신한</t>
-  </si>
-  <si>
     <t>2024-07-05</t>
   </si>
   <si>
@@ -238,37 +226,40 @@
     <t>2024-07-08</t>
   </si>
   <si>
+    <t>2024-06-25</t>
+  </si>
+  <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
     <t>2024-07-23</t>
   </si>
   <si>
-    <t>2024-06-25</t>
+    <t>2024-06-27</t>
   </si>
   <si>
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-06-27</t>
-  </si>
-  <si>
     <t>2024-06-21</t>
   </si>
   <si>
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
     <t>2024-07-26</t>
   </si>
   <si>
     <t>2024-07-11</t>
   </si>
   <si>
-    <t>2024-06-28</t>
+    <t>2024-08-12</t>
   </si>
   <si>
     <t>2024-07-29</t>
-  </si>
-  <si>
-    <t>2024-08-06</t>
   </si>
   <si>
     <t>2024-07-01</t>
@@ -635,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -681,22 +672,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H2">
         <v>1150</v>
@@ -719,10 +710,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -731,19 +722,19 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>48000</v>
+        <v>12000</v>
       </c>
       <c r="I3">
-        <v>1600000</v>
+        <v>6000000</v>
       </c>
       <c r="J3">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -757,28 +748,28 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H4">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I4">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="J4">
         <v>2000</v>
@@ -795,31 +786,31 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H5">
-        <v>8000</v>
+        <v>43200</v>
       </c>
       <c r="I5">
-        <v>4000000</v>
+        <v>2400000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -830,25 +821,25 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H6">
         <v>12000</v>
@@ -868,25 +859,25 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H7">
         <v>130500</v>
@@ -909,10 +900,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -921,19 +912,19 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="H8">
-        <v>43200</v>
+        <v>8000</v>
       </c>
       <c r="I8">
-        <v>2400000</v>
+        <v>4000000</v>
       </c>
       <c r="J8">
-        <v>18000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -947,10 +938,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -959,19 +950,19 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>8000</v>
+        <v>16180</v>
       </c>
       <c r="I9">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -985,10 +976,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -997,19 +988,19 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>16180</v>
+        <v>12900</v>
       </c>
       <c r="I10">
-        <v>1618000</v>
+        <v>6450000</v>
       </c>
       <c r="J10">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1020,72 +1011,72 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>255360</v>
+        <v>54133.66</v>
       </c>
       <c r="I11">
-        <v>7600000</v>
+        <v>1330000</v>
       </c>
       <c r="J11">
-        <v>35000</v>
+        <v>43300</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="H12">
-        <v>9500</v>
+        <v>22400</v>
       </c>
       <c r="I12">
-        <v>4750000</v>
+        <v>1400000</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1096,40 +1087,40 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="H13">
-        <v>12900</v>
+        <v>255360</v>
       </c>
       <c r="I13">
-        <v>6450000</v>
+        <v>7600000</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1140,110 +1131,110 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14">
-        <v>54133.66</v>
+        <v>28960</v>
       </c>
       <c r="I14">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="J14">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H15">
-        <v>22340</v>
+        <v>10640</v>
       </c>
       <c r="I15">
-        <v>2234000</v>
+        <v>7600000</v>
       </c>
       <c r="J15">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H16">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I16">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J16">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1251,113 +1242,113 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="H17">
-        <v>28960</v>
+        <v>17400</v>
       </c>
       <c r="I17">
-        <v>1810000</v>
+        <v>7250000</v>
       </c>
       <c r="J17">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="H18">
-        <v>3455.34</v>
+        <v>35000.001</v>
       </c>
       <c r="I18">
-        <v>1330000</v>
+        <v>23333334</v>
       </c>
       <c r="J18">
-        <v>43300</v>
+        <v>3000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="H19">
-        <v>35000.001</v>
+        <v>3455.34</v>
       </c>
       <c r="I19">
-        <v>23333334</v>
+        <v>1330000</v>
       </c>
       <c r="J19">
-        <v>3000</v>
+        <v>43300</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1365,25 +1356,25 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H20">
-        <v>17400</v>
+        <v>143550</v>
       </c>
       <c r="I20">
         <v>7250000</v>
@@ -1395,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1403,37 +1394,37 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H21">
-        <v>143550</v>
+        <v>29700</v>
       </c>
       <c r="I21">
-        <v>7250000</v>
+        <v>1350000</v>
       </c>
       <c r="J21">
-        <v>60000</v>
+        <v>22000</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1441,69 +1432,69 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H22">
-        <v>29700</v>
+        <v>143550</v>
       </c>
       <c r="I22">
-        <v>1350000</v>
+        <v>7250000</v>
       </c>
       <c r="J22">
-        <v>22000</v>
+        <v>60000</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H23">
-        <v>12500</v>
+        <v>23800</v>
       </c>
       <c r="I23">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="J23">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1514,116 +1505,116 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H24">
-        <v>21850</v>
+        <v>12500</v>
       </c>
       <c r="I24">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="J24">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="H25">
-        <v>8000</v>
+        <v>21850</v>
       </c>
       <c r="I25">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="J25">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26">
-        <v>143550</v>
+        <v>35000.001</v>
       </c>
       <c r="I26">
-        <v>7250000</v>
+        <v>23333334</v>
       </c>
       <c r="J26">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1631,10 +1622,10 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -1643,138 +1634,24 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H27">
-        <v>22100</v>
+        <v>14000</v>
       </c>
       <c r="I27">
-        <v>1300000</v>
+        <v>7000000</v>
       </c>
       <c r="J27">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28">
-        <v>23800</v>
-      </c>
-      <c r="I28">
-        <v>3400000</v>
-      </c>
-      <c r="J28">
-        <v>7000</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29">
-        <v>35000.001</v>
-      </c>
-      <c r="I29">
-        <v>23333334</v>
-      </c>
-      <c r="J29">
-        <v>3000</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30">
-        <v>14000</v>
-      </c>
-      <c r="I30">
-        <v>7000000</v>
-      </c>
-      <c r="J30">
-        <v>2000</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>인수기관</t>
   </si>
@@ -55,9 +55,6 @@
     <t>BNK</t>
   </si>
   <si>
-    <t>KB</t>
-  </si>
-  <si>
     <t>LS</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
     <t>SK</t>
   </si>
   <si>
+    <t>교보</t>
+  </si>
+  <si>
     <t>대신</t>
   </si>
   <si>
@@ -88,48 +88,42 @@
     <t>한국</t>
   </si>
   <si>
-    <t>현대차</t>
-  </si>
-  <si>
     <t>2024-06-14</t>
   </si>
   <si>
-    <t>2024-06-11</t>
-  </si>
-  <si>
     <t>2024-07-02</t>
   </si>
   <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
     <t>2024-07-03</t>
   </si>
   <si>
     <t>2024-06-13</t>
   </si>
   <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
     <t>2024-06-20</t>
   </si>
   <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
+    <t>2024-07-25</t>
   </si>
   <si>
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
     <t>2024-07-22</t>
   </si>
   <si>
@@ -142,45 +136,45 @@
     <t>에스오에스랩</t>
   </si>
   <si>
-    <t>KB제29호스팩</t>
-  </si>
-  <si>
     <t>이베스트스팩6호</t>
   </si>
   <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
     <t>에이치브이엠</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>시프트업</t>
   </si>
   <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>미래에셋비전스팩6호</t>
   </si>
   <si>
+    <t>산일전기</t>
+  </si>
+  <si>
     <t>이노스페이스</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>산일전기</t>
+    <t>아이빔테크놀로지</t>
   </si>
   <si>
     <t>하스</t>
   </si>
   <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>한국제15호스팩</t>
   </si>
   <si>
-    <t>에이치엠씨제7호스팩</t>
-  </si>
-  <si>
     <t>엘에스</t>
   </si>
   <si>
@@ -211,49 +202,52 @@
     <t>한국, 제이피모간회사 서울지점, NH, 신한</t>
   </si>
   <si>
+    <t>미래, 삼성</t>
+  </si>
+  <si>
     <t>미래, 신한</t>
   </si>
   <si>
-    <t>미래, 삼성</t>
-  </si>
-  <si>
     <t>2024-07-05</t>
   </si>
   <si>
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
     <t>2024-07-08</t>
   </si>
   <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
     <t>2024-06-25</t>
   </si>
   <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
-    <t>2024-07-23</t>
+    <t>2024-07-30</t>
   </si>
   <si>
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
     <t>2024-06-21</t>
   </si>
   <si>
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>2024-07-26</t>
+  </si>
+  <si>
     <t>2024-06-28</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
   </si>
   <si>
     <t>2024-08-12</t>
@@ -626,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -672,22 +666,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2">
         <v>1150</v>
@@ -710,28 +704,28 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I3">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="J3">
         <v>2000</v>
@@ -748,28 +742,28 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H4">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I4">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="J4">
         <v>2000</v>
@@ -783,25 +777,25 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H5">
         <v>43200</v>
@@ -821,40 +815,40 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H6">
-        <v>12000</v>
+        <v>130500</v>
       </c>
       <c r="I6">
-        <v>6000000</v>
+        <v>7250000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -862,37 +856,37 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>130500</v>
+        <v>8000</v>
       </c>
       <c r="I7">
-        <v>7250000</v>
+        <v>4000000</v>
       </c>
       <c r="J7">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -900,10 +894,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -912,16 +906,16 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="H8">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="I8">
-        <v>4000000</v>
+        <v>5800000</v>
       </c>
       <c r="J8">
         <v>2000</v>
@@ -938,10 +932,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -950,10 +944,10 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H9">
         <v>16180</v>
@@ -976,10 +970,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -988,19 +982,19 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>12900</v>
+        <v>22400</v>
       </c>
       <c r="I10">
-        <v>6450000</v>
+        <v>1400000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1014,37 +1008,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>54133.66</v>
+        <v>12900</v>
       </c>
       <c r="I11">
-        <v>1330000</v>
+        <v>6450000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>2000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1052,37 +1046,37 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12">
-        <v>22400</v>
+        <v>255360</v>
       </c>
       <c r="I12">
-        <v>1400000</v>
+        <v>7600000</v>
       </c>
       <c r="J12">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1090,37 +1084,37 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="H13">
-        <v>255360</v>
+        <v>54133.66</v>
       </c>
       <c r="I13">
-        <v>7600000</v>
+        <v>1330000</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>43300</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1128,10 +1122,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -1140,19 +1134,19 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H14">
-        <v>28960</v>
+        <v>22340</v>
       </c>
       <c r="I14">
-        <v>1810000</v>
+        <v>2234000</v>
       </c>
       <c r="J14">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1166,22 +1160,22 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H15">
         <v>10640</v>
@@ -1204,10 +1198,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -1216,19 +1210,19 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>22340</v>
+        <v>28960</v>
       </c>
       <c r="I16">
-        <v>2234000</v>
+        <v>1810000</v>
       </c>
       <c r="J16">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1242,37 +1236,37 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="H17">
-        <v>17400</v>
+        <v>3455.34</v>
       </c>
       <c r="I17">
-        <v>7250000</v>
+        <v>1330000</v>
       </c>
       <c r="J17">
-        <v>60000</v>
+        <v>43300</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1280,37 +1274,37 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H18">
-        <v>35000.001</v>
+        <v>17400</v>
       </c>
       <c r="I18">
-        <v>23333334</v>
+        <v>7250000</v>
       </c>
       <c r="J18">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1318,37 +1312,37 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19">
+        <v>35000.001</v>
+      </c>
+      <c r="I19">
+        <v>23333334</v>
+      </c>
+      <c r="J19">
+        <v>3000</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19">
-        <v>3455.34</v>
-      </c>
-      <c r="I19">
-        <v>1330000</v>
-      </c>
-      <c r="J19">
-        <v>43300</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1356,22 +1350,22 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>64</v>
       </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H20">
         <v>143550</v>
@@ -1394,10 +1388,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -1406,10 +1400,10 @@
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H21">
         <v>29700</v>
@@ -1432,37 +1426,37 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H22">
-        <v>143550</v>
+        <v>23800</v>
       </c>
       <c r="I22">
-        <v>7250000</v>
+        <v>3400000</v>
       </c>
       <c r="J22">
-        <v>60000</v>
+        <v>7000</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1470,10 +1464,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -1482,19 +1476,19 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H23">
-        <v>23800</v>
+        <v>12500</v>
       </c>
       <c r="I23">
-        <v>3400000</v>
+        <v>6250000</v>
       </c>
       <c r="J23">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1508,37 +1502,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H24">
-        <v>12500</v>
+        <v>21850</v>
       </c>
       <c r="I24">
-        <v>6250000</v>
+        <v>2000000</v>
       </c>
       <c r="J24">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1549,34 +1543,34 @@
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H25">
-        <v>21850</v>
+        <v>143550</v>
       </c>
       <c r="I25">
-        <v>2000000</v>
+        <v>7250000</v>
       </c>
       <c r="J25">
-        <v>11500</v>
+        <v>60000</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>95</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1584,22 +1578,22 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H26">
         <v>35000.001</v>
@@ -1615,44 +1609,6 @@
       </c>
       <c r="L26">
         <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H27">
-        <v>14000</v>
-      </c>
-      <c r="I27">
-        <v>7000000</v>
-      </c>
-      <c r="J27">
-        <v>2000</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="82">
   <si>
     <t>인수기관</t>
   </si>
@@ -106,30 +106,33 @@
     <t>2024-07-03</t>
   </si>
   <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
     <t>2024-07-18</t>
   </si>
   <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-07-25</t>
+    <t>2024-08-06</t>
   </si>
   <si>
     <t>2024-07-22</t>
   </si>
   <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
     <t>이베스트스팩6호</t>
   </si>
   <si>
@@ -151,36 +154,39 @@
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
     <t>산일전기</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
     <t>하스</t>
   </si>
   <si>
-    <t>아이빔테크놀로지</t>
+    <t>유라클</t>
   </si>
   <si>
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
-    <t>유라클</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
     <t>넥스트바이오메디컬</t>
   </si>
   <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
     <t>엘에스</t>
   </si>
   <si>
@@ -190,12 +196,12 @@
     <t>한국, 제이피모간회사 서울지점, NH, 신한</t>
   </si>
   <si>
+    <t>미래, 신한</t>
+  </si>
+  <si>
     <t>미래, 삼성</t>
   </si>
   <si>
-    <t>미래, 신한</t>
-  </si>
-  <si>
     <t>2024-07-05</t>
   </si>
   <si>
@@ -205,27 +211,27 @@
     <t>2024-07-08</t>
   </si>
   <si>
+    <t>2024-06-25</t>
+  </si>
+  <si>
     <t>2024-07-23</t>
   </si>
   <si>
-    <t>2024-06-25</t>
-  </si>
-  <si>
     <t>2024-08-13</t>
   </si>
   <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
     <t>2024-08-12</t>
   </si>
   <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
     <t>2024-07-12</t>
   </si>
   <si>
@@ -244,13 +250,16 @@
     <t>2024-08-19</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-07-31</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
     <t>2024-08-20</t>
+  </si>
+  <si>
+    <t>2024-08-21</t>
   </si>
 </sst>
 </file>
@@ -608,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -657,19 +666,19 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -695,7 +704,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -704,10 +713,10 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3">
         <v>12000</v>
@@ -733,19 +742,19 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>130500</v>
@@ -771,7 +780,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -780,10 +789,10 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H5">
         <v>43200</v>
@@ -809,7 +818,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -818,10 +827,10 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H6">
         <v>8000</v>
@@ -847,7 +856,7 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -856,10 +865,10 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>11600</v>
@@ -885,7 +894,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -894,7 +903,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -920,37 +929,37 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H9">
-        <v>255360</v>
+        <v>22400</v>
       </c>
       <c r="I9">
-        <v>7600000</v>
+        <v>1400000</v>
       </c>
       <c r="J9">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -958,37 +967,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="H10">
-        <v>22400</v>
+        <v>54133.66</v>
       </c>
       <c r="I10">
-        <v>1400000</v>
+        <v>1330000</v>
       </c>
       <c r="J10">
-        <v>16000</v>
+        <v>43300</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -999,34 +1008,34 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H11">
-        <v>54133.66</v>
+        <v>255360</v>
       </c>
       <c r="I11">
-        <v>1330000</v>
+        <v>7600000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>35000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1037,7 +1046,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1046,10 +1055,10 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>50781.225</v>
@@ -1072,37 +1081,37 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I13">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1110,37 +1119,37 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
         <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H14">
-        <v>28960</v>
+        <v>10640</v>
       </c>
       <c r="I14">
-        <v>1810000</v>
+        <v>7600000</v>
       </c>
       <c r="J14">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1151,7 +1160,7 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1160,19 +1169,19 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>22340</v>
+        <v>28960</v>
       </c>
       <c r="I15">
-        <v>2234000</v>
+        <v>1810000</v>
       </c>
       <c r="J15">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1186,7 +1195,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -1195,10 +1204,10 @@
         <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
         <v>24</v>
@@ -1227,19 +1236,19 @@
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>17400</v>
@@ -1265,19 +1274,19 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H18">
         <v>143550</v>
@@ -1303,7 +1312,7 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
@@ -1312,19 +1321,19 @@
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19">
-        <v>29700</v>
+        <v>15771</v>
       </c>
       <c r="I19">
-        <v>1350000</v>
+        <v>751000</v>
       </c>
       <c r="J19">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1341,7 +1350,7 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
@@ -1350,19 +1359,19 @@
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H20">
-        <v>15771</v>
+        <v>29700</v>
       </c>
       <c r="I20">
-        <v>751000</v>
+        <v>1350000</v>
       </c>
       <c r="J20">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1379,7 +1388,7 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -1388,10 +1397,10 @@
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21">
         <v>21700</v>
@@ -1417,19 +1426,19 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22">
         <v>143550</v>
@@ -1455,7 +1464,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -1464,10 +1473,10 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H23">
         <v>29000</v>
@@ -1482,6 +1491,44 @@
         <v>0</v>
       </c>
       <c r="L23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24">
+        <v>13000</v>
+      </c>
+      <c r="I24">
+        <v>1000000</v>
+      </c>
+      <c r="J24">
+        <v>13000</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="88">
   <si>
     <t>인수기관</t>
   </si>
@@ -73,9 +73,15 @@
     <t>삼성</t>
   </si>
   <si>
+    <t>신영</t>
+  </si>
+  <si>
     <t>신한</t>
   </si>
   <si>
+    <t>유진</t>
+  </si>
+  <si>
     <t>제이피모간회사</t>
   </si>
   <si>
@@ -91,18 +97,21 @@
     <t>2024-07-02</t>
   </si>
   <si>
+    <t>2024-06-19</t>
+  </si>
+  <si>
     <t>2024-07-16</t>
   </si>
   <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
     <t>2024-08-01</t>
   </si>
   <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
     <t>2024-07-03</t>
   </si>
   <si>
@@ -121,63 +130,69 @@
     <t>2024-06-24</t>
   </si>
   <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
     <t>이베스트스팩6호</t>
   </si>
   <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
     <t>교보16호스팩</t>
   </si>
   <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
     <t>하스</t>
   </si>
   <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
     <t>유라클</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -202,12 +217,18 @@
     <t>미래, 삼성</t>
   </si>
   <si>
+    <t>신영, 유진</t>
+  </si>
+  <si>
     <t>2024-07-05</t>
   </si>
   <si>
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
     <t>2024-07-08</t>
   </si>
   <si>
@@ -226,31 +247,28 @@
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
+    <t>2024-08-16</t>
   </si>
   <si>
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>2024-06-28</t>
+    <t>2024-08-22</t>
   </si>
   <si>
     <t>2024-07-29</t>
   </si>
   <si>
     <t>2024-08-19</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
   </si>
   <si>
     <t>2024-07-31</t>
@@ -617,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -663,22 +681,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -701,10 +719,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -713,19 +731,19 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H3">
-        <v>12000</v>
+        <v>43200</v>
       </c>
       <c r="I3">
-        <v>6000000</v>
+        <v>2400000</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -739,22 +757,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H4">
         <v>130500</v>
@@ -777,10 +795,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -789,19 +807,19 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H5">
-        <v>43200</v>
+        <v>12000</v>
       </c>
       <c r="I5">
-        <v>2400000</v>
+        <v>6000000</v>
       </c>
       <c r="J5">
-        <v>18000</v>
+        <v>2000</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -815,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -827,10 +845,10 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6">
         <v>8000</v>
@@ -853,10 +871,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -865,10 +883,10 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H7">
         <v>11600</v>
@@ -891,10 +909,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -903,19 +921,19 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="H8">
-        <v>16180</v>
+        <v>13000</v>
       </c>
       <c r="I8">
-        <v>1618000</v>
+        <v>6500000</v>
       </c>
       <c r="J8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -926,34 +944,34 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>22400</v>
+        <v>16180</v>
       </c>
       <c r="I9">
-        <v>1400000</v>
+        <v>1618000</v>
       </c>
       <c r="J9">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -967,22 +985,22 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H10">
         <v>54133.66</v>
@@ -1005,22 +1023,22 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H11">
         <v>255360</v>
@@ -1043,10 +1061,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1055,10 +1073,10 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H12">
         <v>50781.225</v>
@@ -1078,34 +1096,34 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>22340</v>
+        <v>22400</v>
       </c>
       <c r="I13">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="J13">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1119,37 +1137,37 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="H14">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I14">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J14">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1163,69 +1181,69 @@
         <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="H15">
-        <v>28960</v>
+        <v>10640</v>
       </c>
       <c r="I15">
-        <v>1810000</v>
+        <v>7600000</v>
       </c>
       <c r="J15">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H16">
-        <v>3455.34</v>
+        <v>28960</v>
       </c>
       <c r="I16">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="J16">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1233,37 +1251,37 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H17">
-        <v>17400</v>
+        <v>22800</v>
       </c>
       <c r="I17">
-        <v>7250000</v>
+        <v>1500000</v>
       </c>
       <c r="J17">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1271,75 +1289,75 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="H18">
-        <v>143550</v>
+        <v>3455.34</v>
       </c>
       <c r="I18">
-        <v>7250000</v>
+        <v>1330000</v>
       </c>
       <c r="J18">
-        <v>60000</v>
+        <v>43300</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19">
-        <v>15771</v>
+        <v>17400</v>
       </c>
       <c r="I19">
-        <v>751000</v>
+        <v>7250000</v>
       </c>
       <c r="J19">
-        <v>21000</v>
+        <v>60000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1347,37 +1365,37 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H20">
-        <v>29700</v>
+        <v>1200</v>
       </c>
       <c r="I20">
-        <v>1350000</v>
+        <v>1500000</v>
       </c>
       <c r="J20">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1385,37 +1403,37 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
       </c>
       <c r="H21">
-        <v>21700</v>
+        <v>143550</v>
       </c>
       <c r="I21">
-        <v>1400000</v>
+        <v>7250000</v>
       </c>
       <c r="J21">
-        <v>15500</v>
+        <v>60000</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1423,37 +1441,37 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H22">
-        <v>143550</v>
+        <v>29700</v>
       </c>
       <c r="I22">
-        <v>7250000</v>
+        <v>1350000</v>
       </c>
       <c r="J22">
-        <v>60000</v>
+        <v>22000</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1461,10 +1479,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -1473,19 +1491,19 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H23">
-        <v>29000</v>
+        <v>15771</v>
       </c>
       <c r="I23">
-        <v>1000000</v>
+        <v>751000</v>
       </c>
       <c r="J23">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1496,39 +1514,153 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24">
+        <v>21700</v>
+      </c>
+      <c r="I24">
+        <v>1400000</v>
+      </c>
+      <c r="J24">
+        <v>15500</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" t="s">
-        <v>81</v>
-      </c>
-      <c r="H24">
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25">
+        <v>29000</v>
+      </c>
+      <c r="I25">
+        <v>1000000</v>
+      </c>
+      <c r="J25">
+        <v>29000</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26">
+        <v>143550</v>
+      </c>
+      <c r="I26">
+        <v>7250000</v>
+      </c>
+      <c r="J26">
+        <v>60000</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27">
         <v>13000</v>
       </c>
-      <c r="I24">
+      <c r="I27">
         <v>1000000</v>
       </c>
-      <c r="J24">
+      <c r="J27">
         <v>13000</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
   <si>
     <t>인수기관</t>
   </si>
@@ -100,6 +100,9 @@
     <t>2024-06-19</t>
   </si>
   <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
     <t>2024-07-16</t>
   </si>
   <si>
@@ -130,9 +133,6 @@
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
     <t>2024-07-22</t>
   </si>
   <si>
@@ -148,6 +148,9 @@
     <t>에이치브이엠</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>시프트업</t>
   </si>
   <si>
@@ -223,6 +226,9 @@
     <t>2024-07-05</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-07-19</t>
   </si>
   <si>
@@ -247,13 +253,13 @@
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
     <t>2024-07-12</t>
   </si>
   <si>
     <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>2024-08-23</t>
   </si>
   <si>
     <t>2024-07-11</t>
@@ -635,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -687,16 +693,16 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -731,10 +737,10 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>43200</v>
@@ -757,37 +763,37 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4">
-        <v>130500</v>
+        <v>23972.04</v>
       </c>
       <c r="I4">
-        <v>7250000</v>
+        <v>1566800</v>
       </c>
       <c r="J4">
-        <v>60000</v>
+        <v>15300</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -795,42 +801,42 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5">
-        <v>12000</v>
+        <v>130500</v>
       </c>
       <c r="I5">
-        <v>6000000</v>
+        <v>7250000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -839,22 +845,22 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="H6">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="J6">
         <v>2000</v>
@@ -868,7 +874,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
@@ -877,22 +883,22 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>11600</v>
+        <v>8000</v>
       </c>
       <c r="I7">
-        <v>5800000</v>
+        <v>4000000</v>
       </c>
       <c r="J7">
         <v>2000</v>
@@ -906,7 +912,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -915,22 +921,22 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H8">
-        <v>13000</v>
+        <v>11600</v>
       </c>
       <c r="I8">
-        <v>6500000</v>
+        <v>5800000</v>
       </c>
       <c r="J8">
         <v>2000</v>
@@ -959,19 +965,19 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="H9">
-        <v>16180</v>
+        <v>13000</v>
       </c>
       <c r="I9">
-        <v>1618000</v>
+        <v>6500000</v>
       </c>
       <c r="J9">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -982,7 +988,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
@@ -991,31 +997,31 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>54133.66</v>
+        <v>16180</v>
       </c>
       <c r="I10">
-        <v>1330000</v>
+        <v>1618000</v>
       </c>
       <c r="J10">
-        <v>43300</v>
+        <v>10000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1035,25 +1041,25 @@
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="H11">
-        <v>255360</v>
+        <v>54133.66</v>
       </c>
       <c r="I11">
-        <v>7600000</v>
+        <v>1330000</v>
       </c>
       <c r="J11">
-        <v>35000</v>
+        <v>43300</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1070,28 +1076,28 @@
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12">
-        <v>50781.225</v>
+        <v>255360</v>
       </c>
       <c r="I12">
-        <v>3077650</v>
+        <v>7600000</v>
       </c>
       <c r="J12">
-        <v>16500</v>
+        <v>35000</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1099,7 +1105,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>53</v>
@@ -1111,19 +1117,19 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="H13">
-        <v>22400</v>
+        <v>50781.225</v>
       </c>
       <c r="I13">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="J13">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1134,34 +1140,34 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H14">
-        <v>22340</v>
+        <v>22400</v>
       </c>
       <c r="I14">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="J14">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1175,37 +1181,37 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="H15">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I15">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J15">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1213,42 +1219,42 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H16">
-        <v>28960</v>
+        <v>10640</v>
       </c>
       <c r="I16">
-        <v>1810000</v>
+        <v>7600000</v>
       </c>
       <c r="J16">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
@@ -1257,22 +1263,22 @@
         <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>22800</v>
+        <v>28960</v>
       </c>
       <c r="I17">
-        <v>1500000</v>
+        <v>1810000</v>
       </c>
       <c r="J17">
         <v>16000</v>
@@ -1281,45 +1287,45 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="H18">
-        <v>3455.34</v>
+        <v>22800</v>
       </c>
       <c r="I18">
-        <v>1330000</v>
+        <v>1500000</v>
       </c>
       <c r="J18">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1327,151 +1333,151 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
         <v>26</v>
       </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
       <c r="H19">
-        <v>17400</v>
+        <v>3455.34</v>
       </c>
       <c r="I19">
-        <v>7250000</v>
+        <v>1330000</v>
       </c>
       <c r="J19">
-        <v>60000</v>
+        <v>43300</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
         <v>82</v>
       </c>
       <c r="H20">
-        <v>1200</v>
+        <v>17400</v>
       </c>
       <c r="I20">
-        <v>1500000</v>
+        <v>7250000</v>
       </c>
       <c r="J20">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H21">
-        <v>143550</v>
+        <v>1200</v>
       </c>
       <c r="I21">
-        <v>7250000</v>
+        <v>1500000</v>
       </c>
       <c r="J21">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H22">
-        <v>29700</v>
+        <v>143550</v>
       </c>
       <c r="I22">
-        <v>1350000</v>
+        <v>7250000</v>
       </c>
       <c r="J22">
-        <v>22000</v>
+        <v>60000</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1479,7 +1485,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>58</v>
@@ -1491,19 +1497,19 @@
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H23">
-        <v>15771</v>
+        <v>29700</v>
       </c>
       <c r="I23">
-        <v>751000</v>
+        <v>1350000</v>
       </c>
       <c r="J23">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1514,34 +1520,34 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="H24">
-        <v>21700</v>
+        <v>15771</v>
       </c>
       <c r="I24">
-        <v>1400000</v>
+        <v>751000</v>
       </c>
       <c r="J24">
-        <v>15500</v>
+        <v>21000</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1552,34 +1558,34 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
         <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H25">
-        <v>29000</v>
+        <v>21700</v>
       </c>
       <c r="I25">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="J25">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1593,37 +1599,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H26">
-        <v>143550</v>
+        <v>29000</v>
       </c>
       <c r="I26">
-        <v>7250000</v>
+        <v>1000000</v>
       </c>
       <c r="J26">
-        <v>60000</v>
+        <v>29000</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1631,36 +1637,74 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27">
+        <v>143550</v>
+      </c>
+      <c r="I27">
+        <v>7250000</v>
+      </c>
+      <c r="J27">
+        <v>60000</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="E27" t="s">
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
         <v>25</v>
       </c>
-      <c r="F27" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27">
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28">
         <v>13000</v>
       </c>
-      <c r="I27">
+      <c r="I28">
         <v>1000000</v>
       </c>
-      <c r="J27">
+      <c r="J28">
         <v>13000</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>인수기관</t>
   </si>
@@ -97,9 +97,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -112,48 +109,42 @@
     <t>2024-08-01</t>
   </si>
   <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
     <t>2024-08-09</t>
   </si>
   <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>2024-06-20</t>
+    <t>2024-08-08</t>
   </si>
   <si>
     <t>2024-07-18</t>
   </si>
   <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
     <t>2024-07-25</t>
   </si>
   <si>
     <t>2024-06-24</t>
   </si>
   <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
     <t>2024-07-22</t>
   </si>
   <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
     <t>이베스트스팩6호</t>
   </si>
   <si>
-    <t>에이치브이엠</t>
+    <t>시프트업</t>
   </si>
   <si>
     <t>이엔셀</t>
   </si>
   <si>
-    <t>시프트업</t>
-  </si>
-  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
@@ -163,24 +154,21 @@
     <t>교보16호스팩</t>
   </si>
   <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
     <t>대신밸런스제18호스팩</t>
   </si>
   <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
   </si>
   <si>
     <t>산일전기</t>
   </si>
   <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -190,12 +178,12 @@
     <t>M83</t>
   </si>
   <si>
+    <t>유라클</t>
+  </si>
+  <si>
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
-    <t>유라클</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -214,9 +202,6 @@
     <t>한국, 제이피모간회사 서울지점, NH, 신한</t>
   </si>
   <si>
-    <t>미래, 신한</t>
-  </si>
-  <si>
     <t>미래, 삼성</t>
   </si>
   <si>
@@ -232,21 +217,18 @@
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-07-08</t>
+  </si>
+  <si>
     <t>2024-08-14</t>
   </si>
   <si>
-    <t>2024-07-08</t>
-  </si>
-  <si>
-    <t>2024-06-25</t>
+    <t>2024-08-13</t>
   </si>
   <si>
     <t>2024-07-23</t>
   </si>
   <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -256,25 +238,22 @@
     <t>2024-07-12</t>
   </si>
   <si>
-    <t>2024-06-28</t>
+    <t>2024-07-11</t>
   </si>
   <si>
     <t>2024-08-23</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
     <t>2024-07-26</t>
   </si>
   <si>
     <t>2024-08-22</t>
   </si>
   <si>
+    <t>2024-08-19</t>
+  </si>
+  <si>
     <t>2024-07-29</t>
-  </si>
-  <si>
-    <t>2024-08-19</t>
   </si>
   <si>
     <t>2024-07-31</t>
@@ -641,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -690,19 +669,19 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -725,37 +704,37 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H3">
-        <v>43200</v>
+        <v>130500</v>
       </c>
       <c r="I3">
-        <v>2400000</v>
+        <v>7250000</v>
       </c>
       <c r="J3">
-        <v>18000</v>
+        <v>60000</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -763,10 +742,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -775,10 +754,10 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>23972.04</v>
@@ -801,66 +780,66 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H5">
-        <v>130500</v>
+        <v>12000</v>
       </c>
       <c r="I5">
-        <v>7250000</v>
+        <v>6000000</v>
       </c>
       <c r="J5">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I6">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="J6">
         <v>2000</v>
@@ -874,31 +853,31 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="H7">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="I7">
-        <v>4000000</v>
+        <v>5800000</v>
       </c>
       <c r="J7">
         <v>2000</v>
@@ -912,34 +891,34 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>11600</v>
+        <v>16180</v>
       </c>
       <c r="I8">
-        <v>5800000</v>
+        <v>1618000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -956,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -965,10 +944,10 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>13000</v>
@@ -988,34 +967,34 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>16180</v>
+        <v>50781.225</v>
       </c>
       <c r="I10">
-        <v>1618000</v>
+        <v>3077650</v>
       </c>
       <c r="J10">
-        <v>10000</v>
+        <v>16500</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1029,37 +1008,37 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>54133.66</v>
+        <v>22400</v>
       </c>
       <c r="I11">
-        <v>1330000</v>
+        <v>1400000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1067,22 +1046,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H12">
         <v>255360</v>
@@ -1102,34 +1081,34 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="H13">
-        <v>50781.225</v>
+        <v>22340</v>
       </c>
       <c r="I13">
-        <v>3077650</v>
+        <v>2234000</v>
       </c>
       <c r="J13">
-        <v>16500</v>
+        <v>10000</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1140,40 +1119,40 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="H14">
-        <v>22400</v>
+        <v>10640</v>
       </c>
       <c r="I14">
-        <v>1400000</v>
+        <v>7600000</v>
       </c>
       <c r="J14">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1181,10 +1160,10 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -1193,19 +1172,19 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H15">
-        <v>22340</v>
+        <v>28960</v>
       </c>
       <c r="I15">
-        <v>2234000</v>
+        <v>1810000</v>
       </c>
       <c r="J15">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1216,104 +1195,104 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H16">
-        <v>10640</v>
+        <v>22800</v>
       </c>
       <c r="I16">
-        <v>7600000</v>
+        <v>1500000</v>
       </c>
       <c r="J16">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H17">
-        <v>28960</v>
+        <v>17400</v>
       </c>
       <c r="I17">
-        <v>1810000</v>
+        <v>7250000</v>
       </c>
       <c r="J17">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H18">
-        <v>22800</v>
+        <v>1200</v>
       </c>
       <c r="I18">
         <v>1500000</v>
@@ -1325,191 +1304,191 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" t="s">
         <v>74</v>
       </c>
-      <c r="G19" t="s">
-        <v>26</v>
-      </c>
       <c r="H19">
-        <v>3455.34</v>
+        <v>143550</v>
       </c>
       <c r="I19">
-        <v>1330000</v>
+        <v>7250000</v>
       </c>
       <c r="J19">
-        <v>43300</v>
+        <v>60000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
         <v>65</v>
       </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" t="s">
-        <v>82</v>
-      </c>
       <c r="H20">
-        <v>17400</v>
+        <v>15771</v>
       </c>
       <c r="I20">
-        <v>7250000</v>
+        <v>751000</v>
       </c>
       <c r="J20">
-        <v>60000</v>
+        <v>21000</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H21">
-        <v>1200</v>
+        <v>29700</v>
       </c>
       <c r="I21">
-        <v>1500000</v>
+        <v>1350000</v>
       </c>
       <c r="J21">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
         <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H22">
-        <v>143550</v>
+        <v>21700</v>
       </c>
       <c r="I22">
-        <v>7250000</v>
+        <v>1400000</v>
       </c>
       <c r="J22">
-        <v>60000</v>
+        <v>15500</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H23">
-        <v>29700</v>
+        <v>29000</v>
       </c>
       <c r="I23">
-        <v>1350000</v>
+        <v>1000000</v>
       </c>
       <c r="J23">
-        <v>22000</v>
+        <v>29000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1520,34 +1499,34 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H24">
-        <v>15771</v>
+        <v>13000</v>
       </c>
       <c r="I24">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="J24">
-        <v>21000</v>
+        <v>13000</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1558,154 +1537,40 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
         <v>60</v>
       </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H25">
-        <v>21700</v>
+        <v>143550</v>
       </c>
       <c r="I25">
-        <v>1400000</v>
+        <v>7250000</v>
       </c>
       <c r="J25">
-        <v>15500</v>
+        <v>60000</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26">
-        <v>29000</v>
-      </c>
-      <c r="I26">
-        <v>1000000</v>
-      </c>
-      <c r="J26">
-        <v>29000</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27">
-        <v>143550</v>
-      </c>
-      <c r="I27">
-        <v>7250000</v>
-      </c>
-      <c r="J27">
-        <v>60000</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
         <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28">
-        <v>13000</v>
-      </c>
-      <c r="I28">
-        <v>1000000</v>
-      </c>
-      <c r="J28">
-        <v>13000</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="80">
   <si>
     <t>인수기관</t>
   </si>
@@ -124,9 +124,6 @@
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>2024-08-06</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>하스</t>
-  </si>
-  <si>
     <t>M83</t>
   </si>
   <si>
@@ -230,9 +224,6 @@
   </si>
   <si>
     <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>2024-06-27</t>
   </si>
   <si>
     <t>2024-07-12</t>
@@ -620,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -669,19 +660,19 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -707,19 +698,19 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H3">
         <v>130500</v>
@@ -745,7 +736,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -754,10 +745,10 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H4">
         <v>23972.04</v>
@@ -783,7 +774,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -792,10 +783,10 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H5">
         <v>12000</v>
@@ -821,7 +812,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -859,7 +850,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -868,10 +859,10 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H7">
         <v>11600</v>
@@ -897,7 +888,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -906,7 +897,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -935,7 +926,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -944,10 +935,10 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>13000</v>
@@ -973,7 +964,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -982,10 +973,10 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>50781.225</v>
@@ -1011,7 +1002,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1020,7 +1011,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -1049,19 +1040,19 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>255360</v>
@@ -1084,37 +1075,37 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="H13">
-        <v>22340</v>
+        <v>10640</v>
       </c>
       <c r="I13">
-        <v>2234000</v>
+        <v>7600000</v>
       </c>
       <c r="J13">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1122,66 +1113,66 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I14">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J14">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="H15">
-        <v>28960</v>
+        <v>22800</v>
       </c>
       <c r="I15">
-        <v>1810000</v>
+        <v>1500000</v>
       </c>
       <c r="J15">
         <v>16000</v>
@@ -1190,159 +1181,159 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H16">
-        <v>22800</v>
+        <v>17400</v>
       </c>
       <c r="I16">
-        <v>1500000</v>
+        <v>7250000</v>
       </c>
       <c r="J16">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>95</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
       </c>
       <c r="H17">
-        <v>17400</v>
+        <v>1200</v>
       </c>
       <c r="I17">
-        <v>7250000</v>
+        <v>1500000</v>
       </c>
       <c r="J17">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H18">
-        <v>1200</v>
+        <v>143550</v>
       </c>
       <c r="I18">
-        <v>1500000</v>
+        <v>7250000</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H19">
-        <v>143550</v>
+        <v>15771</v>
       </c>
       <c r="I19">
-        <v>7250000</v>
+        <v>751000</v>
       </c>
       <c r="J19">
-        <v>60000</v>
+        <v>21000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1353,7 +1344,7 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -1362,19 +1353,19 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="H20">
-        <v>15771</v>
+        <v>29700</v>
       </c>
       <c r="I20">
-        <v>751000</v>
+        <v>1350000</v>
       </c>
       <c r="J20">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1385,34 +1376,34 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H21">
-        <v>29700</v>
+        <v>21700</v>
       </c>
       <c r="I21">
-        <v>1350000</v>
+        <v>1400000</v>
       </c>
       <c r="J21">
-        <v>22000</v>
+        <v>15500</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1423,34 +1414,34 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H22">
-        <v>21700</v>
+        <v>29000</v>
       </c>
       <c r="I22">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="J22">
-        <v>15500</v>
+        <v>29000</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1464,10 +1455,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -1476,19 +1467,19 @@
         <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="I23">
         <v>1000000</v>
       </c>
       <c r="J23">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1502,74 +1493,36 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
         <v>58</v>
       </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H24">
-        <v>13000</v>
+        <v>143550</v>
       </c>
       <c r="I24">
-        <v>1000000</v>
+        <v>7250000</v>
       </c>
       <c r="J24">
-        <v>13000</v>
+        <v>60000</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25">
-        <v>143550</v>
-      </c>
-      <c r="I25">
-        <v>7250000</v>
-      </c>
-      <c r="J25">
-        <v>60000</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
         <v>33</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>인수기관</t>
   </si>
@@ -115,21 +115,24 @@
     <t>2024-08-09</t>
   </si>
   <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
     <t>2024-08-08</t>
   </si>
   <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
     <t>2024-07-25</t>
   </si>
   <si>
+    <t>2024-08-21</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
@@ -157,27 +160,30 @@
     <t>대신밸런스제18호스팩</t>
   </si>
   <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
+    <t>아이스크림미디어</t>
+  </si>
+  <si>
     <t>M83</t>
   </si>
   <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
     <t>유라클</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -217,15 +223,18 @@
     <t>2024-08-14</t>
   </si>
   <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
+    <t>2024-08-26</t>
+  </si>
+  <si>
     <t>2024-07-12</t>
   </si>
   <si>
@@ -241,19 +250,19 @@
     <t>2024-08-22</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-08-19</t>
   </si>
   <si>
-    <t>2024-07-29</t>
+    <t>2024-08-30</t>
   </si>
   <si>
     <t>2024-07-31</t>
   </si>
   <si>
     <t>2024-08-20</t>
-  </si>
-  <si>
-    <t>2024-08-21</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -660,19 +669,19 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H2">
         <v>8000</v>
@@ -698,19 +707,19 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>130500</v>
@@ -736,7 +745,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -745,10 +754,10 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>23972.04</v>
@@ -774,7 +783,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -783,10 +792,10 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>12000</v>
@@ -812,7 +821,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -821,7 +830,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>35</v>
@@ -850,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -859,10 +868,10 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H7">
         <v>11600</v>
@@ -888,7 +897,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -897,7 +906,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -926,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -935,10 +944,10 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>13000</v>
@@ -964,34 +973,34 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>50781.225</v>
+        <v>255360</v>
       </c>
       <c r="I10">
-        <v>3077650</v>
+        <v>7600000</v>
       </c>
       <c r="J10">
-        <v>16500</v>
+        <v>35000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1002,7 +1011,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -1011,7 +1020,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
         <v>27</v>
@@ -1040,34 +1049,34 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H12">
-        <v>255360</v>
+        <v>50781.225</v>
       </c>
       <c r="I12">
-        <v>7600000</v>
+        <v>3077650</v>
       </c>
       <c r="J12">
-        <v>35000</v>
+        <v>16500</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1075,37 +1084,37 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H13">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I13">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1113,227 +1122,227 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
         <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H14">
-        <v>22340</v>
+        <v>10640</v>
       </c>
       <c r="I14">
-        <v>2234000</v>
+        <v>7600000</v>
       </c>
       <c r="J14">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H15">
-        <v>22800</v>
+        <v>78720</v>
       </c>
       <c r="I15">
-        <v>1500000</v>
+        <v>2460000</v>
       </c>
       <c r="J15">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H16">
-        <v>17400</v>
+        <v>22800</v>
       </c>
       <c r="I16">
-        <v>7250000</v>
+        <v>1500000</v>
       </c>
       <c r="J16">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
       </c>
       <c r="H17">
-        <v>1200</v>
+        <v>17400</v>
       </c>
       <c r="I17">
-        <v>1500000</v>
+        <v>7250000</v>
       </c>
       <c r="J17">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H18">
-        <v>143550</v>
+        <v>1200</v>
       </c>
       <c r="I18">
-        <v>7250000</v>
+        <v>1500000</v>
       </c>
       <c r="J18">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H19">
-        <v>15771</v>
+        <v>143550</v>
       </c>
       <c r="I19">
-        <v>751000</v>
+        <v>7250000</v>
       </c>
       <c r="J19">
-        <v>21000</v>
+        <v>60000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1344,7 +1353,7 @@
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -1356,7 +1365,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H20">
         <v>29700</v>
@@ -1376,34 +1385,34 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H21">
-        <v>21700</v>
+        <v>15771</v>
       </c>
       <c r="I21">
-        <v>1400000</v>
+        <v>751000</v>
       </c>
       <c r="J21">
-        <v>15500</v>
+        <v>21000</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1414,34 +1423,34 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H22">
-        <v>29000</v>
+        <v>21700</v>
       </c>
       <c r="I22">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="J22">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1455,10 +1464,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -1467,19 +1476,19 @@
         <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H23">
-        <v>13000</v>
+        <v>29000</v>
       </c>
       <c r="I23">
         <v>1000000</v>
       </c>
       <c r="J23">
-        <v>13000</v>
+        <v>29000</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1493,36 +1502,74 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>13000</v>
+      </c>
+      <c r="I24">
+        <v>1000000</v>
+      </c>
+      <c r="J24">
+        <v>13000</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24">
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25">
         <v>143550</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>7250000</v>
       </c>
-      <c r="J24">
+      <c r="J25">
         <v>60000</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>33</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="71">
   <si>
     <t>인수기관</t>
   </si>
@@ -52,9 +52,6 @@
     <t>인수비율</t>
   </si>
   <si>
-    <t>LS</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -76,15 +73,9 @@
     <t>신영</t>
   </si>
   <si>
-    <t>신한</t>
-  </si>
-  <si>
     <t>유진</t>
   </si>
   <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
     <t>키움</t>
   </si>
   <si>
@@ -94,15 +85,12 @@
     <t>한국</t>
   </si>
   <si>
-    <t>2024-07-02</t>
+    <t>2024-07-16</t>
   </si>
   <si>
     <t>2024-08-12</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -136,18 +124,12 @@
     <t>2024-08-07</t>
   </si>
   <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>시프트업</t>
+    <t>엔에이치스팩31호</t>
   </si>
   <si>
     <t>이엔셀</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
@@ -163,12 +145,12 @@
     <t>산일전기</t>
   </si>
   <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -187,36 +169,24 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
     <t>넥스트바이오메디컬</t>
   </si>
   <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>엘에스</t>
-  </si>
-  <si>
-    <t>한국, 제이피모간회사 서울지점, NH</t>
-  </si>
-  <si>
-    <t>한국, 제이피모간회사 서울지점, NH, 신한</t>
-  </si>
-  <si>
     <t>미래, 삼성</t>
   </si>
   <si>
     <t>신영, 유진</t>
   </si>
   <si>
-    <t>2024-07-05</t>
+    <t>2024-07-19</t>
   </si>
   <si>
     <t>2024-08-16</t>
   </si>
   <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
     <t>2024-07-08</t>
   </si>
   <si>
@@ -235,16 +205,10 @@
     <t>2024-08-26</t>
   </si>
   <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
+    <t>2024-07-26</t>
   </si>
   <si>
     <t>2024-08-23</t>
-  </si>
-  <si>
-    <t>2024-07-26</t>
   </si>
   <si>
     <t>2024-08-22</t>
@@ -620,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -666,28 +630,28 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H2">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I2">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="J2">
         <v>2000</v>
@@ -701,40 +665,40 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
         <v>64</v>
       </c>
-      <c r="G3" t="s">
-        <v>74</v>
-      </c>
       <c r="H3">
-        <v>130500</v>
+        <v>23972.04</v>
       </c>
       <c r="I3">
-        <v>7250000</v>
+        <v>1566800</v>
       </c>
       <c r="J3">
-        <v>60000</v>
+        <v>15300</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -742,10 +706,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -754,19 +718,19 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>23972.04</v>
+        <v>8000</v>
       </c>
       <c r="I4">
-        <v>1566800</v>
+        <v>4000000</v>
       </c>
       <c r="J4">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -777,31 +741,31 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>12000</v>
+        <v>11600</v>
       </c>
       <c r="I5">
-        <v>6000000</v>
+        <v>5800000</v>
       </c>
       <c r="J5">
         <v>2000</v>
@@ -815,34 +779,34 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>8000</v>
+        <v>16180</v>
       </c>
       <c r="I6">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -856,10 +820,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -868,16 +832,16 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H7">
-        <v>11600</v>
+        <v>13000</v>
       </c>
       <c r="I7">
-        <v>5800000</v>
+        <v>6500000</v>
       </c>
       <c r="J7">
         <v>2000</v>
@@ -894,37 +858,37 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="H8">
-        <v>16180</v>
+        <v>255360</v>
       </c>
       <c r="I8">
-        <v>1618000</v>
+        <v>7600000</v>
       </c>
       <c r="J8">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -932,10 +896,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -944,19 +908,19 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H9">
-        <v>13000</v>
+        <v>50781.225</v>
       </c>
       <c r="I9">
-        <v>6500000</v>
+        <v>3077650</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>16500</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -967,40 +931,40 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="H10">
-        <v>255360</v>
+        <v>22400</v>
       </c>
       <c r="I10">
-        <v>7600000</v>
+        <v>1400000</v>
       </c>
       <c r="J10">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1008,37 +972,37 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H11">
-        <v>22400</v>
+        <v>10640</v>
       </c>
       <c r="I11">
-        <v>1400000</v>
+        <v>7600000</v>
       </c>
       <c r="J11">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1046,10 +1010,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1058,19 +1022,19 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>50781.225</v>
+        <v>22340</v>
       </c>
       <c r="I12">
-        <v>3077650</v>
+        <v>2234000</v>
       </c>
       <c r="J12">
-        <v>16500</v>
+        <v>10000</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1081,34 +1045,34 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="H13">
-        <v>22340</v>
+        <v>78720</v>
       </c>
       <c r="I13">
-        <v>2234000</v>
+        <v>2460000</v>
       </c>
       <c r="J13">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1122,113 +1086,113 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H14">
-        <v>10640</v>
+        <v>22800</v>
       </c>
       <c r="I14">
-        <v>7600000</v>
+        <v>1500000</v>
       </c>
       <c r="J14">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H15">
-        <v>78720</v>
+        <v>1200</v>
       </c>
       <c r="I15">
-        <v>2460000</v>
+        <v>1500000</v>
       </c>
       <c r="J15">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H16">
-        <v>22800</v>
+        <v>29700</v>
       </c>
       <c r="I16">
-        <v>1500000</v>
+        <v>1350000</v>
       </c>
       <c r="J16">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1236,37 +1200,37 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H17">
-        <v>17400</v>
+        <v>15771</v>
       </c>
       <c r="I17">
-        <v>7250000</v>
+        <v>751000</v>
       </c>
       <c r="J17">
-        <v>60000</v>
+        <v>21000</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1274,37 +1238,37 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H18">
-        <v>1200</v>
+        <v>21700</v>
       </c>
       <c r="I18">
-        <v>1500000</v>
+        <v>1400000</v>
       </c>
       <c r="J18">
-        <v>16000</v>
+        <v>15500</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1312,265 +1276,75 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>143550</v>
+        <v>13000</v>
       </c>
       <c r="I19">
-        <v>7250000</v>
+        <v>1000000</v>
       </c>
       <c r="J19">
-        <v>60000</v>
+        <v>13000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H20">
-        <v>29700</v>
+        <v>29000</v>
       </c>
       <c r="I20">
-        <v>1350000</v>
+        <v>1000000</v>
       </c>
       <c r="J20">
-        <v>22000</v>
+        <v>29000</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
         <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21">
-        <v>15771</v>
-      </c>
-      <c r="I21">
-        <v>751000</v>
-      </c>
-      <c r="J21">
-        <v>21000</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22">
-        <v>21700</v>
-      </c>
-      <c r="I22">
-        <v>1400000</v>
-      </c>
-      <c r="J22">
-        <v>15500</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23">
-        <v>29000</v>
-      </c>
-      <c r="I23">
-        <v>1000000</v>
-      </c>
-      <c r="J23">
-        <v>29000</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24">
-        <v>13000</v>
-      </c>
-      <c r="I24">
-        <v>1000000</v>
-      </c>
-      <c r="J24">
-        <v>13000</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25">
-        <v>143550</v>
-      </c>
-      <c r="I25">
-        <v>7250000</v>
-      </c>
-      <c r="J25">
-        <v>60000</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
   <si>
     <t>인수기관</t>
   </si>
@@ -85,21 +85,18 @@
     <t>한국</t>
   </si>
   <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
     <t>2024-07-16</t>
   </si>
   <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
     <t>2024-08-01</t>
   </si>
   <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
     <t>2024-08-09</t>
   </si>
   <si>
@@ -124,21 +121,18 @@
     <t>2024-08-07</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
     <t>SK증권제13호스팩</t>
   </si>
   <si>
     <t>교보16호스팩</t>
   </si>
   <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
     <t>대신밸런스제18호스팩</t>
   </si>
   <si>
@@ -181,15 +175,12 @@
     <t>신영, 유진</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>2024-07-08</t>
-  </si>
-  <si>
     <t>2024-08-14</t>
   </si>
   <si>
@@ -205,10 +196,10 @@
     <t>2024-08-26</t>
   </si>
   <si>
+    <t>2024-08-23</t>
+  </si>
+  <si>
     <t>2024-07-26</t>
-  </si>
-  <si>
-    <t>2024-08-23</t>
   </si>
   <si>
     <t>2024-08-22</t>
@@ -584,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -633,7 +624,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -642,19 +633,19 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>12000</v>
+        <v>23972.04</v>
       </c>
       <c r="I2">
-        <v>6000000</v>
+        <v>1566800</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>15300</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -671,7 +662,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -680,19 +671,19 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H3">
-        <v>23972.04</v>
+        <v>12000</v>
       </c>
       <c r="I3">
-        <v>1566800</v>
+        <v>6000000</v>
       </c>
       <c r="J3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -709,7 +700,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -718,10 +709,10 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>8000</v>
@@ -747,7 +738,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -756,10 +747,10 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>11600</v>
@@ -785,7 +776,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -794,19 +785,19 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="H6">
-        <v>16180</v>
+        <v>13000</v>
       </c>
       <c r="I6">
-        <v>1618000</v>
+        <v>6500000</v>
       </c>
       <c r="J6">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -817,40 +808,40 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H7">
-        <v>13000</v>
+        <v>255360</v>
       </c>
       <c r="I7">
-        <v>6500000</v>
+        <v>7600000</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -861,34 +852,34 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H8">
-        <v>255360</v>
+        <v>50781.225</v>
       </c>
       <c r="I8">
-        <v>7600000</v>
+        <v>3077650</v>
       </c>
       <c r="J8">
-        <v>35000</v>
+        <v>16500</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -896,10 +887,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -908,19 +899,19 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="H9">
-        <v>50781.225</v>
+        <v>22400</v>
       </c>
       <c r="I9">
-        <v>3077650</v>
+        <v>1400000</v>
       </c>
       <c r="J9">
-        <v>16500</v>
+        <v>16000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -931,40 +922,40 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="H10">
-        <v>22400</v>
+        <v>10640</v>
       </c>
       <c r="I10">
-        <v>1400000</v>
+        <v>7600000</v>
       </c>
       <c r="J10">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -972,37 +963,37 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H11">
-        <v>10640</v>
+        <v>22340</v>
       </c>
       <c r="I11">
-        <v>7600000</v>
+        <v>2234000</v>
       </c>
       <c r="J11">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1013,7 +1004,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1022,19 +1013,19 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="H12">
-        <v>22340</v>
+        <v>78720</v>
       </c>
       <c r="I12">
-        <v>2234000</v>
+        <v>2460000</v>
       </c>
       <c r="J12">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1045,66 +1036,66 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
         <v>62</v>
       </c>
-      <c r="G13" t="s">
-        <v>68</v>
-      </c>
       <c r="H13">
-        <v>78720</v>
+        <v>22800</v>
       </c>
       <c r="I13">
-        <v>2460000</v>
+        <v>1500000</v>
       </c>
       <c r="J13">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H14">
-        <v>22800</v>
+        <v>1200</v>
       </c>
       <c r="I14">
         <v>1500000</v>
@@ -1116,45 +1107,45 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15">
-        <v>1200</v>
+        <v>29700</v>
       </c>
       <c r="I15">
-        <v>1500000</v>
+        <v>1350000</v>
       </c>
       <c r="J15">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1165,7 +1156,7 @@
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1174,19 +1165,19 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="H16">
-        <v>29700</v>
+        <v>15771</v>
       </c>
       <c r="I16">
-        <v>1350000</v>
+        <v>751000</v>
       </c>
       <c r="J16">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1197,34 +1188,34 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H17">
-        <v>15771</v>
+        <v>21700</v>
       </c>
       <c r="I17">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="J17">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1235,34 +1226,34 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="H18">
-        <v>21700</v>
+        <v>13000</v>
       </c>
       <c r="I18">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="J18">
-        <v>15500</v>
+        <v>13000</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1276,10 +1267,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -1288,62 +1279,24 @@
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="H19">
-        <v>13000</v>
+        <v>29000</v>
       </c>
       <c r="I19">
         <v>1000000</v>
       </c>
       <c r="J19">
-        <v>13000</v>
+        <v>29000</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20">
-        <v>29000</v>
-      </c>
-      <c r="I20">
-        <v>1000000</v>
-      </c>
-      <c r="J20">
-        <v>29000</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="72">
   <si>
     <t>인수기관</t>
   </si>
@@ -103,6 +103,9 @@
     <t>2024-07-18</t>
   </si>
   <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -112,12 +115,12 @@
     <t>2024-08-21</t>
   </si>
   <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
     <t>2024-07-22</t>
   </si>
   <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
@@ -139,12 +142,15 @@
     <t>산일전기</t>
   </si>
   <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩7호</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -154,12 +160,12 @@
     <t>M83</t>
   </si>
   <si>
+    <t>유라클</t>
+  </si>
+  <si>
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
-    <t>유라클</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
     <t>2024-07-23</t>
   </si>
   <si>
+    <t>2024-09-05</t>
+  </si>
+  <si>
     <t>2024-08-13</t>
   </si>
   <si>
@@ -206,6 +215,9 @@
   </si>
   <si>
     <t>2024-07-29</t>
+  </si>
+  <si>
+    <t>2024-09-11</t>
   </si>
   <si>
     <t>2024-08-19</t>
@@ -575,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -624,7 +636,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -633,10 +645,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>23972.04</v>
@@ -662,7 +674,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -671,10 +683,10 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H3">
         <v>12000</v>
@@ -700,7 +712,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -712,7 +724,7 @@
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>8000</v>
@@ -738,7 +750,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -750,7 +762,7 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H5">
         <v>11600</v>
@@ -776,7 +788,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -785,10 +797,10 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H6">
         <v>13000</v>
@@ -814,19 +826,19 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H7">
         <v>255360</v>
@@ -849,10 +861,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -861,19 +873,19 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="H8">
-        <v>50781.225</v>
+        <v>22400</v>
       </c>
       <c r="I8">
-        <v>3077650</v>
+        <v>1400000</v>
       </c>
       <c r="J8">
-        <v>16500</v>
+        <v>16000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -887,10 +899,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -899,19 +911,19 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="H9">
-        <v>22400</v>
+        <v>15900</v>
       </c>
       <c r="I9">
-        <v>1400000</v>
+        <v>7950000</v>
       </c>
       <c r="J9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -922,40 +934,40 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>10640</v>
+        <v>50781.225</v>
       </c>
       <c r="I10">
-        <v>7600000</v>
+        <v>3077650</v>
       </c>
       <c r="J10">
-        <v>35000</v>
+        <v>16500</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -963,10 +975,10 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -975,7 +987,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -1001,10 +1013,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -1013,10 +1025,10 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H12">
         <v>78720</v>
@@ -1036,66 +1048,66 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H13">
-        <v>22800</v>
+        <v>10640</v>
       </c>
       <c r="I13">
-        <v>1500000</v>
+        <v>7600000</v>
       </c>
       <c r="J13">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H14">
-        <v>1200</v>
+        <v>22800</v>
       </c>
       <c r="I14">
         <v>1500000</v>
@@ -1107,45 +1119,45 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H15">
-        <v>29700</v>
+        <v>1200</v>
       </c>
       <c r="I15">
-        <v>1350000</v>
+        <v>1500000</v>
       </c>
       <c r="J15">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1156,7 +1168,7 @@
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1168,7 +1180,7 @@
         <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H16">
         <v>15771</v>
@@ -1188,34 +1200,34 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H17">
-        <v>21700</v>
+        <v>29700</v>
       </c>
       <c r="I17">
-        <v>1400000</v>
+        <v>1350000</v>
       </c>
       <c r="J17">
-        <v>15500</v>
+        <v>22000</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1226,34 +1238,34 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H18">
-        <v>13000</v>
+        <v>21700</v>
       </c>
       <c r="I18">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="J18">
-        <v>13000</v>
+        <v>15500</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1267,10 +1279,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -1279,24 +1291,62 @@
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="I19">
         <v>1000000</v>
       </c>
       <c r="J19">
+        <v>13000</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20">
         <v>29000</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
+      <c r="I20">
+        <v>1000000</v>
+      </c>
+      <c r="J20">
+        <v>29000</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
   <si>
     <t>인수기관</t>
   </si>
@@ -55,9 +55,6 @@
     <t>NH</t>
   </si>
   <si>
-    <t>SK</t>
-  </si>
-  <si>
     <t>교보</t>
   </si>
   <si>
@@ -85,15 +82,12 @@
     <t>한국</t>
   </si>
   <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-08-12</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-07-15</t>
-  </si>
-  <si>
     <t>2024-08-01</t>
   </si>
   <si>
@@ -103,12 +97,12 @@
     <t>2024-07-18</t>
   </si>
   <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
     <t>2024-09-02</t>
   </si>
   <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
     <t>2024-07-25</t>
   </si>
   <si>
@@ -124,15 +118,12 @@
     <t>2024-08-07</t>
   </si>
   <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
     <t>이엔셀</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
     <t>교보16호스팩</t>
   </si>
   <si>
@@ -145,12 +136,12 @@
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -169,58 +160,58 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
+    <t>넥스트바이오메디컬</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
     <t>미래, 삼성</t>
   </si>
   <si>
     <t>신영, 유진</t>
   </si>
   <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
     <t>2024-08-16</t>
   </si>
   <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
     <t>2024-08-14</t>
   </si>
   <si>
     <t>2024-07-23</t>
   </si>
   <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
     <t>2024-09-05</t>
   </si>
   <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
     <t>2024-08-26</t>
   </si>
   <si>
+    <t>2024-07-26</t>
+  </si>
+  <si>
     <t>2024-08-23</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>2024-08-22</t>
   </si>
   <si>
     <t>2024-07-29</t>
   </si>
   <si>
+    <t>2024-08-19</t>
+  </si>
+  <si>
     <t>2024-09-11</t>
-  </si>
-  <si>
-    <t>2024-08-19</t>
   </si>
   <si>
     <t>2024-08-30</t>
@@ -587,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -633,10 +624,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -645,19 +636,19 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>23972.04</v>
+        <v>12000</v>
       </c>
       <c r="I2">
-        <v>1566800</v>
+        <v>6000000</v>
       </c>
       <c r="J2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -671,10 +662,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -683,19 +674,19 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H3">
-        <v>12000</v>
+        <v>23972.04</v>
       </c>
       <c r="I3">
-        <v>6000000</v>
+        <v>1566800</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>15300</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -709,10 +700,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -721,16 +712,16 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H4">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="I4">
-        <v>4000000</v>
+        <v>5800000</v>
       </c>
       <c r="J4">
         <v>2000</v>
@@ -747,10 +738,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -759,16 +750,16 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5">
-        <v>11600</v>
+        <v>13000</v>
       </c>
       <c r="I5">
-        <v>5800000</v>
+        <v>6500000</v>
       </c>
       <c r="J5">
         <v>2000</v>
@@ -785,107 +776,107 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H6">
-        <v>13000</v>
+        <v>255360</v>
       </c>
       <c r="I6">
-        <v>6500000</v>
+        <v>7600000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="H7">
-        <v>255360</v>
+        <v>22400</v>
       </c>
       <c r="I7">
-        <v>7600000</v>
+        <v>1400000</v>
       </c>
       <c r="J7">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="H8">
-        <v>22400</v>
+        <v>50781.225</v>
       </c>
       <c r="I8">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="J8">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -896,25 +887,25 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H9">
         <v>15900</v>
@@ -937,60 +928,60 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H10">
-        <v>50781.225</v>
+        <v>10640</v>
       </c>
       <c r="I10">
-        <v>3077650</v>
+        <v>7600000</v>
       </c>
       <c r="J10">
-        <v>16500</v>
+        <v>35000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
       </c>
       <c r="H11">
         <v>22340</v>
@@ -1010,25 +1001,25 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H12">
         <v>78720</v>
@@ -1051,37 +1042,37 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
         <v>53</v>
       </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H13">
-        <v>10640</v>
+        <v>22800</v>
       </c>
       <c r="I13">
-        <v>7600000</v>
+        <v>1500000</v>
       </c>
       <c r="J13">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1092,22 +1083,22 @@
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H14">
-        <v>22800</v>
+        <v>1200</v>
       </c>
       <c r="I14">
         <v>1500000</v>
@@ -1119,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1127,69 +1118,69 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H15">
-        <v>1200</v>
+        <v>15771</v>
       </c>
       <c r="I15">
-        <v>1500000</v>
+        <v>751000</v>
       </c>
       <c r="J15">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H16">
-        <v>15771</v>
+        <v>29700</v>
       </c>
       <c r="I16">
-        <v>751000</v>
+        <v>1350000</v>
       </c>
       <c r="J16">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1203,10 +1194,10 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1215,19 +1206,19 @@
         <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H17">
-        <v>29700</v>
+        <v>21700</v>
       </c>
       <c r="I17">
-        <v>1350000</v>
+        <v>1400000</v>
       </c>
       <c r="J17">
-        <v>22000</v>
+        <v>15500</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1241,10 +1232,10 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1253,19 +1244,19 @@
         <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H18">
-        <v>21700</v>
+        <v>29000</v>
       </c>
       <c r="I18">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="J18">
-        <v>15500</v>
+        <v>29000</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1276,25 +1267,25 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H19">
         <v>13000</v>
@@ -1309,44 +1300,6 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20">
-        <v>29000</v>
-      </c>
-      <c r="I20">
-        <v>1000000</v>
-      </c>
-      <c r="J20">
-        <v>29000</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="65">
   <si>
     <t>인수기관</t>
   </si>
@@ -82,9 +82,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -94,15 +91,15 @@
     <t>2024-08-09</t>
   </si>
   <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
     <t>2024-07-18</t>
   </si>
   <si>
     <t>2024-08-08</t>
   </si>
   <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
     <t>2024-07-25</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>2024-08-07</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>이엔셀</t>
   </si>
   <si>
@@ -130,18 +124,18 @@
     <t>대신밸런스제18호스팩</t>
   </si>
   <si>
+    <t>미래에셋비전스팩7호</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>산일전기</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
-    <t>미래에셋비전스팩7호</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -172,46 +166,40 @@
     <t>신영, 유진</t>
   </si>
   <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
     <t>2024-08-16</t>
   </si>
   <si>
     <t>2024-08-14</t>
   </si>
   <si>
+    <t>2024-09-05</t>
+  </si>
+  <si>
     <t>2024-07-23</t>
   </si>
   <si>
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-09-05</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
     <t>2024-08-26</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
     <t>2024-08-22</t>
   </si>
   <si>
+    <t>2024-09-11</t>
+  </si>
+  <si>
     <t>2024-07-29</t>
   </si>
   <si>
     <t>2024-08-19</t>
-  </si>
-  <si>
-    <t>2024-09-11</t>
   </si>
   <si>
     <t>2024-08-30</t>
@@ -578,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -627,7 +615,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -636,19 +624,19 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H2">
-        <v>12000</v>
+        <v>23972.04</v>
       </c>
       <c r="I2">
-        <v>6000000</v>
+        <v>1566800</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>15300</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -659,34 +647,34 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H3">
-        <v>23972.04</v>
+        <v>11600</v>
       </c>
       <c r="I3">
-        <v>1566800</v>
+        <v>5800000</v>
       </c>
       <c r="J3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -697,31 +685,31 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H4">
-        <v>11600</v>
+        <v>13000</v>
       </c>
       <c r="I4">
-        <v>5800000</v>
+        <v>6500000</v>
       </c>
       <c r="J4">
         <v>2000</v>
@@ -735,31 +723,31 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H5">
-        <v>13000</v>
+        <v>15900</v>
       </c>
       <c r="I5">
-        <v>6500000</v>
+        <v>7950000</v>
       </c>
       <c r="J5">
         <v>2000</v>
@@ -776,37 +764,37 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>255360</v>
+        <v>22400</v>
       </c>
       <c r="I6">
-        <v>7600000</v>
+        <v>1400000</v>
       </c>
       <c r="J6">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -814,37 +802,37 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="H7">
-        <v>22400</v>
+        <v>255360</v>
       </c>
       <c r="I7">
-        <v>1400000</v>
+        <v>7600000</v>
       </c>
       <c r="J7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -855,7 +843,7 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -864,10 +852,10 @@
         <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H8">
         <v>50781.225</v>
@@ -887,34 +875,34 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>15900</v>
+        <v>22340</v>
       </c>
       <c r="I9">
-        <v>7950000</v>
+        <v>2234000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -937,13 +925,13 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H10">
         <v>10640</v>
@@ -969,7 +957,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -978,19 +966,19 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H11">
-        <v>22340</v>
+        <v>78720</v>
       </c>
       <c r="I11">
-        <v>2234000</v>
+        <v>2460000</v>
       </c>
       <c r="J11">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1001,66 +989,66 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H12">
-        <v>78720</v>
+        <v>22800</v>
       </c>
       <c r="I12">
-        <v>2460000</v>
+        <v>1500000</v>
       </c>
       <c r="J12">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H13">
-        <v>22800</v>
+        <v>1200</v>
       </c>
       <c r="I13">
         <v>1500000</v>
@@ -1072,45 +1060,45 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H14">
-        <v>1200</v>
+        <v>15771</v>
       </c>
       <c r="I14">
-        <v>1500000</v>
+        <v>751000</v>
       </c>
       <c r="J14">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1121,7 +1109,7 @@
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -1130,19 +1118,19 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H15">
-        <v>15771</v>
+        <v>29700</v>
       </c>
       <c r="I15">
-        <v>751000</v>
+        <v>1350000</v>
       </c>
       <c r="J15">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1153,34 +1141,34 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H16">
-        <v>29700</v>
+        <v>21700</v>
       </c>
       <c r="I16">
-        <v>1350000</v>
+        <v>1400000</v>
       </c>
       <c r="J16">
-        <v>22000</v>
+        <v>15500</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1191,34 +1179,34 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H17">
-        <v>21700</v>
+        <v>29000</v>
       </c>
       <c r="I17">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="J17">
-        <v>15500</v>
+        <v>29000</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1232,10 +1220,10 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1244,62 +1232,24 @@
         <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="I18">
         <v>1000000</v>
       </c>
       <c r="J18">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19">
-        <v>13000</v>
-      </c>
-      <c r="I19">
-        <v>1000000</v>
-      </c>
-      <c r="J19">
-        <v>13000</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
   <si>
     <t>인수기관</t>
   </si>
@@ -94,18 +94,15 @@
     <t>2024-09-02</t>
   </si>
   <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
+    <t>2024-08-21</t>
+  </si>
+  <si>
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>2024-08-21</t>
-  </si>
-  <si>
     <t>2024-08-06</t>
   </si>
   <si>
@@ -127,21 +124,18 @@
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
+    <t>아이스크림미디어</t>
   </si>
   <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>아이스크림미디어</t>
-  </si>
-  <si>
     <t>M83</t>
   </si>
   <si>
@@ -154,15 +148,12 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
     <t>넥스트바이오메디컬</t>
   </si>
   <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>미래, 삼성</t>
-  </si>
-  <si>
     <t>신영, 유진</t>
   </si>
   <si>
@@ -175,18 +166,15 @@
     <t>2024-09-05</t>
   </si>
   <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
     <t>2024-08-13</t>
   </si>
   <si>
+    <t>2024-08-26</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-08-26</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -194,9 +182,6 @@
   </si>
   <si>
     <t>2024-09-11</t>
-  </si>
-  <si>
-    <t>2024-07-29</t>
   </si>
   <si>
     <t>2024-08-19</t>
@@ -566,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -615,7 +600,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -624,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>23972.04</v>
@@ -653,7 +638,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -662,10 +647,10 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>11600</v>
@@ -691,7 +676,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -700,10 +685,10 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H4">
         <v>13000</v>
@@ -729,7 +714,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -738,10 +723,10 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H5">
         <v>15900</v>
@@ -764,10 +749,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -776,19 +761,19 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="H6">
-        <v>22400</v>
+        <v>50781.225</v>
       </c>
       <c r="I6">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="J6">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -802,69 +787,69 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>255360</v>
+        <v>22400</v>
       </c>
       <c r="I7">
-        <v>7600000</v>
+        <v>1400000</v>
       </c>
       <c r="J7">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H8">
-        <v>50781.225</v>
+        <v>78720</v>
       </c>
       <c r="I8">
-        <v>3077650</v>
+        <v>2460000</v>
       </c>
       <c r="J8">
-        <v>16500</v>
+        <v>32000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -881,7 +866,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -890,10 +875,10 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9">
         <v>22340</v>
@@ -913,186 +898,186 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H10">
-        <v>10640</v>
+        <v>22800</v>
       </c>
       <c r="I10">
-        <v>7600000</v>
+        <v>1500000</v>
       </c>
       <c r="J10">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H11">
-        <v>78720</v>
+        <v>1200</v>
       </c>
       <c r="I11">
-        <v>2460000</v>
+        <v>1500000</v>
       </c>
       <c r="J11">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="H12">
-        <v>22800</v>
+        <v>15771</v>
       </c>
       <c r="I12">
-        <v>1500000</v>
+        <v>751000</v>
       </c>
       <c r="J12">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
       </c>
       <c r="H13">
-        <v>1200</v>
+        <v>29700</v>
       </c>
       <c r="I13">
-        <v>1500000</v>
+        <v>1350000</v>
       </c>
       <c r="J13">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H14">
-        <v>15771</v>
+        <v>21700</v>
       </c>
       <c r="I14">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="J14">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1103,34 +1088,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H15">
-        <v>29700</v>
+        <v>13000</v>
       </c>
       <c r="I15">
-        <v>1350000</v>
+        <v>1000000</v>
       </c>
       <c r="J15">
-        <v>22000</v>
+        <v>13000</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1141,115 +1126,39 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H16">
-        <v>21700</v>
+        <v>29000</v>
       </c>
       <c r="I16">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
       <c r="J16">
-        <v>15500</v>
+        <v>29000</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17">
-        <v>29000</v>
-      </c>
-      <c r="I17">
-        <v>1000000</v>
-      </c>
-      <c r="J17">
-        <v>29000</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18">
-        <v>13000</v>
-      </c>
-      <c r="I18">
-        <v>1000000</v>
-      </c>
-      <c r="J18">
-        <v>13000</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
         <v>100</v>
       </c>
     </row>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
   <si>
     <t>인수기관</t>
   </si>
@@ -88,6 +88,9 @@
     <t>2024-08-01</t>
   </si>
   <si>
+    <t>2024-09-09</t>
+  </si>
+  <si>
     <t>2024-08-09</t>
   </si>
   <si>
@@ -106,9 +109,6 @@
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
     <t>2024-08-07</t>
   </si>
   <si>
@@ -118,6 +118,9 @@
     <t>교보16호스팩</t>
   </si>
   <si>
+    <t>아이언디바이스</t>
+  </si>
+  <si>
     <t>대신밸런스제18호스팩</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t>유라클</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -160,6 +160,9 @@
     <t>2024-08-16</t>
   </si>
   <si>
+    <t>2024-09-12</t>
+  </si>
+  <si>
     <t>2024-08-14</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
     <t>2024-08-23</t>
   </si>
   <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
     <t>2024-08-22</t>
   </si>
   <si>
@@ -188,9 +194,6 @@
   </si>
   <si>
     <t>2024-08-30</t>
-  </si>
-  <si>
-    <t>2024-07-31</t>
   </si>
   <si>
     <t>2024-08-20</t>
@@ -612,7 +615,7 @@
         <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H2">
         <v>23972.04</v>
@@ -647,10 +650,10 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>11600</v>
@@ -688,16 +691,16 @@
         <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="I4">
-        <v>6500000</v>
+        <v>3000000</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -708,7 +711,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -717,22 +720,22 @@
         <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>15900</v>
+        <v>13000</v>
       </c>
       <c r="I5">
-        <v>7950000</v>
+        <v>6500000</v>
       </c>
       <c r="J5">
         <v>2000</v>
@@ -764,16 +767,16 @@
         <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>50781.225</v>
+        <v>15900</v>
       </c>
       <c r="I6">
-        <v>3077650</v>
+        <v>7950000</v>
       </c>
       <c r="J6">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -787,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -799,19 +802,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="H7">
-        <v>22400</v>
+        <v>50781.225</v>
       </c>
       <c r="I7">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="J7">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -822,34 +825,34 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>78720</v>
+        <v>22400</v>
       </c>
       <c r="I8">
-        <v>2460000</v>
+        <v>1400000</v>
       </c>
       <c r="J8">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -878,16 +881,16 @@
         <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="H9">
-        <v>22340</v>
+        <v>78720</v>
       </c>
       <c r="I9">
-        <v>2234000</v>
+        <v>2460000</v>
       </c>
       <c r="J9">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -898,51 +901,51 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>22800</v>
+        <v>22340</v>
       </c>
       <c r="I10">
-        <v>1500000</v>
+        <v>2234000</v>
       </c>
       <c r="J10">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -954,10 +957,10 @@
         <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H11">
-        <v>1200</v>
+        <v>22800</v>
       </c>
       <c r="I11">
         <v>1500000</v>
@@ -969,45 +972,45 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H12">
-        <v>15771</v>
+        <v>1200</v>
       </c>
       <c r="I12">
-        <v>751000</v>
+        <v>1500000</v>
       </c>
       <c r="J12">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1027,19 +1030,19 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="H13">
-        <v>29700</v>
+        <v>15771</v>
       </c>
       <c r="I13">
-        <v>1350000</v>
+        <v>751000</v>
       </c>
       <c r="J13">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1053,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1065,10 +1068,10 @@
         <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14">
         <v>21700</v>
@@ -1091,7 +1094,7 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
@@ -1103,10 +1106,10 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H15">
         <v>13000</v>
@@ -1144,7 +1147,7 @@
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16">
         <v>29000</v>

--- a/datasets/form3.xlsx
+++ b/datasets/form3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>인수기관</t>
   </si>
@@ -52,6 +52,9 @@
     <t>인수비율</t>
   </si>
   <si>
+    <t>KB</t>
+  </si>
+  <si>
     <t>NH</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>한국</t>
   </si>
   <si>
+    <t>2024-09-10</t>
+  </si>
+  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -112,6 +118,9 @@
     <t>2024-08-07</t>
   </si>
   <si>
+    <t>KB제30호스팩</t>
+  </si>
+  <si>
     <t>이엔셀</t>
   </si>
   <si>
@@ -157,6 +166,9 @@
     <t>신영, 유진</t>
   </si>
   <si>
+    <t>2024-09-13</t>
+  </si>
+  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -176,6 +188,9 @@
   </si>
   <si>
     <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
   </si>
   <si>
     <t>2024-08-23</t>
@@ -554,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -600,10 +615,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -612,19 +627,19 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H2">
-        <v>23972.04</v>
+        <v>10000</v>
       </c>
       <c r="I2">
-        <v>1566800</v>
+        <v>5000000</v>
       </c>
       <c r="J2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -638,10 +653,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -650,19 +665,19 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H3">
-        <v>11600</v>
+        <v>23972.04</v>
       </c>
       <c r="I3">
-        <v>5800000</v>
+        <v>1566800</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>15300</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -676,10 +691,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -688,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
         <v>55</v>
       </c>
       <c r="H4">
-        <v>21000</v>
+        <v>11600</v>
       </c>
       <c r="I4">
-        <v>3000000</v>
+        <v>5800000</v>
       </c>
       <c r="J4">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -711,34 +726,34 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="I5">
-        <v>6500000</v>
+        <v>3000000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -752,10 +767,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -764,16 +779,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6">
-        <v>15900</v>
+        <v>13000</v>
       </c>
       <c r="I6">
-        <v>7950000</v>
+        <v>6500000</v>
       </c>
       <c r="J6">
         <v>2000</v>
@@ -787,34 +802,34 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H7">
-        <v>50781.225</v>
+        <v>15900</v>
       </c>
       <c r="I7">
-        <v>3077650</v>
+        <v>7950000</v>
       </c>
       <c r="J7">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -825,34 +840,34 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="H8">
-        <v>22400</v>
+        <v>50781.225</v>
       </c>
       <c r="I8">
-        <v>1400000</v>
+        <v>3077650</v>
       </c>
       <c r="J8">
-        <v>16000</v>
+        <v>16500</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -866,10 +881,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -878,19 +893,19 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H9">
-        <v>78720</v>
+        <v>22400</v>
       </c>
       <c r="I9">
-        <v>2460000</v>
+        <v>1400000</v>
       </c>
       <c r="J9">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -901,34 +916,34 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="H10">
-        <v>22340</v>
+        <v>78720</v>
       </c>
       <c r="I10">
-        <v>2234000</v>
+        <v>2460000</v>
       </c>
       <c r="J10">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -942,37 +957,37 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H11">
-        <v>22800</v>
+        <v>22340</v>
       </c>
       <c r="I11">
-        <v>1500000</v>
+        <v>2234000</v>
       </c>
       <c r="J11">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -980,25 +995,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H12">
-        <v>1200</v>
+        <v>22800</v>
       </c>
       <c r="I12">
         <v>1500000</v>
@@ -1010,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1018,37 +1033,37 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H13">
-        <v>15771</v>
+        <v>1200</v>
       </c>
       <c r="I13">
-        <v>751000</v>
+        <v>1500000</v>
       </c>
       <c r="J13">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1056,10 +1071,10 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -1068,19 +1083,19 @@
         <v>20</v>
       </c>
       <c r="F14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
         <v>51</v>
       </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
       <c r="H14">
-        <v>21700</v>
+        <v>15771</v>
       </c>
       <c r="I14">
-        <v>1400000</v>
+        <v>751000</v>
       </c>
       <c r="J14">
-        <v>15500</v>
+        <v>21000</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1094,10 +1109,10 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -1106,19 +1121,19 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="H15">
-        <v>13000</v>
+        <v>21700</v>
       </c>
       <c r="I15">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="J15">
-        <v>13000</v>
+        <v>15500</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1129,39 +1144,77 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="I16">
         <v>1000000</v>
       </c>
       <c r="J16">
+        <v>13000</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17">
         <v>29000</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="I17">
+        <v>1000000</v>
+      </c>
+      <c r="J17">
+        <v>29000</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>100</v>
       </c>
     </row>
